--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="770">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -903,6 +903,7 @@
 rest_home = Rest home level
 hospital = Hospital level
 dementia = Dementia care
+psychogeriatric = Psychogeriatric care
 none = No level was identified
 unsure = Not sure</t>
   </si>
@@ -934,20 +935,6 @@
 separated = Separated or divorced
 partnered_independent = Married or partnered, partner lives independently
 partnered_both_care = Married or partnered, both have significant care needs
-other = Other
-unsure = Not sure
-prefer_not_to_say = Prefer not to say</t>
-  </si>
-  <si>
-    <t>f2</t>
-  </si>
-  <si>
-    <t>Do they own a home, or have an interest in a home?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes = Yes
-no = No
-village = They live in a retirement village
 other = Other
 unsure = Not sure
 prefer_not_to_say = Prefer not to say</t>
@@ -1194,24 +1181,6 @@
 actively_looking = We're actively looking for somewhere
 urgent = A place may be needed urgently
 unsure = Not sure</t>
-  </si>
-  <si>
-    <t>rc2</t>
-  </si>
-  <si>
-    <t>If a formal assessment has identified a level of care, what level was identified?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rest_home = Rest-home level
-hospital = Hospital level
-dementia = Dementia care
-psychogeriatric = Psychogeriatric care
-other = Another level
-none = No formal level has been identified
-unsure = Not sure</t>
-  </si>
-  <si>
-    <t>q19 in completed, receiving, reassessment or rc1 is assessment_identified</t>
   </si>
   <si>
     <t>rc3</t>
@@ -2264,7 +2233,7 @@
     <t>residential-assessment</t>
   </si>
   <si>
-    <t>(q23 is residential_care or trigger has considering_residential or q8 has residential_care or q6 is residential_care) and (rc2 not answered or rc2 in none, unsure, other)</t>
+    <t>(q23 is residential_care or trigger has considering_residential or q8 has residential_care or q6 is residential_care) and (q19_level not answered or q19_level in none, unsure, home_support)</t>
   </si>
   <si>
     <t>Ask how an assessment for residential care is arranged</t>
@@ -2288,7 +2257,7 @@
     <t>residential-search</t>
   </si>
   <si>
-    <t>rc1 in assessment_identified, actively_looking, urgent and rc2 in rest_home, hospital, dementia, psychogeriatric</t>
+    <t>rc1 in assessment_identified, actively_looking, urgent and q19_level in rest_home, hospital, dementia, psychogeriatric</t>
   </si>
   <si>
     <t>Shortlist care homes that provide the assessed level of care</t>
@@ -3456,7 +3425,7 @@
         <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>94</v>
@@ -3464,21 +3433,21 @@
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>79</v>
@@ -3486,10 +3455,10 @@
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>83</v>
@@ -3497,10 +3466,10 @@
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3532,336 +3501,336 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -5735,10 +5704,10 @@
         <v>225</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>1</v>
@@ -5764,7 +5733,7 @@
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>71</v>
@@ -5776,10 +5745,10 @@
         <v>111</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>229</v>
+        <v>1</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>230</v>
@@ -5811,22 +5780,22 @@
         <v>231</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1</v>
+        <v>234</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>1</v>
@@ -5841,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>1</v>
@@ -5852,7 +5821,7 @@
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>75</v>
@@ -5861,16 +5830,16 @@
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>1</v>
@@ -5885,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>239</v>
+        <v>1</v>
       </c>
       <c r="M39" s="4" t="s">
         <v>1</v>
@@ -5899,7 +5868,7 @@
         <v>240</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>1</v>
@@ -5949,19 +5918,19 @@
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>244</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>245</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>1</v>
+        <v>246</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>1</v>
@@ -5984,28 +5953,28 @@
     </row>
     <row r="42" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>1</v>
@@ -6037,7 +6006,7 @@
         <v>79</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>251</v>
@@ -6046,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>1</v>
@@ -6064,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>1</v>
@@ -6081,16 +6050,16 @@
         <v>79</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>254</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>1</v>
@@ -6108,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="N44" s="4" t="s">
         <v>1</v>
@@ -6125,13 +6094,13 @@
         <v>79</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>257</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>258</v>
@@ -6213,19 +6182,19 @@
         <v>79</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>263</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>264</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>1</v>
@@ -6257,19 +6226,19 @@
         <v>79</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>266</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>267</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>1</v>
@@ -6339,22 +6308,22 @@
         <v>271</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>111</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>1</v>
@@ -6380,7 +6349,7 @@
     </row>
     <row r="51" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>83</v>
@@ -6389,19 +6358,19 @@
         <v>83</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>275</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>1</v>
@@ -6427,10 +6396,10 @@
         <v>276</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>111</v>
@@ -6460,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>1</v>
@@ -6468,28 +6437,28 @@
     </row>
     <row r="53" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="4" t="s">
+      <c r="F53" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>282</v>
-      </c>
       <c r="H53" s="4" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>1</v>
@@ -6512,7 +6481,7 @@
     </row>
     <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>87</v>
@@ -6524,19 +6493,19 @@
         <v>111</v>
       </c>
       <c r="E54" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>285</v>
-      </c>
       <c r="H54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>109</v>
@@ -6556,7 +6525,7 @@
     </row>
     <row r="55" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>87</v>
@@ -6568,10 +6537,10 @@
         <v>111</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>1</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>288</v>
@@ -6603,28 +6572,28 @@
         <v>289</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>291</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>1</v>
+        <v>292</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>109</v>
@@ -6644,25 +6613,25 @@
     </row>
     <row r="57" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>295</v>
+        <v>1</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>1</v>
@@ -6671,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>1</v>
@@ -6691,7 +6660,7 @@
         <v>296</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>1</v>
@@ -6712,7 +6681,7 @@
         <v>299</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>109</v>
@@ -6735,13 +6704,13 @@
         <v>300</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>301</v>
@@ -6750,19 +6719,19 @@
         <v>302</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>1</v>
@@ -6776,7 +6745,7 @@
     </row>
     <row r="60" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>91</v>
@@ -6785,25 +6754,25 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>305</v>
+        <v>1</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>306</v>
+        <v>1</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>210</v>
+        <v>1</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>1</v>
@@ -6818,94 +6787,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N61" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N62" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="61" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:10" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:10" x14ac:dyDescent="0.25"/>
     <row r="64" spans="4:10" x14ac:dyDescent="0.25"/>
     <row r="65" spans="4:10" x14ac:dyDescent="0.25"/>
@@ -7080,50 +6963,50 @@
         <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>324</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7131,16 +7014,16 @@
         <v>79</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7151,13 +7034,13 @@
         <v>84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7168,13 +7051,13 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7407,282 +7290,282 @@
         <v>50</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>341</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>373</v>
-      </c>
       <c r="D15" s="4" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7903,278 +7786,278 @@
         <v>41</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>163</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>409</v>
-      </c>
       <c r="M3" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>418</v>
-      </c>
       <c r="L4" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>428</v>
-      </c>
       <c r="L5" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>436</v>
-      </c>
       <c r="L6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="K7" s="4" t="s">
         <v>1</v>
       </c>
@@ -8182,163 +8065,163 @@
         <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>455</v>
-      </c>
       <c r="M8" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="K9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>465</v>
-      </c>
       <c r="M9" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>474</v>
-      </c>
       <c r="L10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="K11" s="4" t="s">
         <v>1</v>
       </c>
@@ -8346,121 +8229,121 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="K12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>492</v>
-      </c>
       <c r="M12" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>1</v>
@@ -8469,197 +8352,197 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="K15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>515</v>
-      </c>
       <c r="M15" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="L16" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>524</v>
-      </c>
       <c r="M16" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="L17" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>535</v>
-      </c>
       <c r="M17" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>543</v>
-      </c>
       <c r="L18" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -8671,36 +8554,36 @@
         <v>1</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>1</v>
@@ -8712,323 +8595,323 @@
         <v>1</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>564</v>
-      </c>
       <c r="M21" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="J22" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>574</v>
-      </c>
       <c r="L22" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="L23" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>583</v>
-      </c>
       <c r="M23" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>606</v>
-      </c>
       <c r="L26" s="4" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="L27" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>616</v>
-      </c>
       <c r="M27" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>1</v>
@@ -9043,33 +8926,33 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>1</v>
@@ -9084,7 +8967,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -9304,197 +9187,197 @@
         <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="7:7" x14ac:dyDescent="0.25"/>
@@ -9716,207 +9599,207 @@
         <v>41</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="770">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="771">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -125,6 +125,12 @@
     <t>one per line, as value = Label. The value is what conditions use: lower-case letters, numbers and underscores.</t>
   </si>
   <si>
+    <t>Option descriptions</t>
+  </si>
+  <si>
+    <t>value = Label | A short description. When every option of a single-choice question has a description, families see the question as cards, and choosing a card moves on.</t>
+  </si>
+  <si>
     <t>Unsure answers</t>
   </si>
   <si>
@@ -179,10 +185,10 @@
     <t>change</t>
   </si>
   <si>
-    <t>What has changed?</t>
-  </si>
-  <si>
-    <t>Most families come to us because something has changed. Choose everything that applies; it helps us show you only the questions that matter.</t>
+    <t>What has brought you here?</t>
+  </si>
+  <si>
+    <t>Sometimes something changes suddenly. Other times, you may simply be planning ahead. Select the reason that best describes your situation.</t>
   </si>
   <si>
     <t>s1</t>
@@ -203,7 +209,7 @@
     <t>Hospital or recent discharge</t>
   </si>
   <si>
-    <t>trigger has hospital or q8 has recent_hospital_admission_or_discharge or q9 has hospital_admission_or_emergency_department_visit or q6 is in_hospital</t>
+    <t>trigger is hospital or q8 has recent_hospital_admission_or_discharge or q9 has hospital_admission_or_emergency_department_visit or q6 is in_hospital</t>
   </si>
   <si>
     <t>s3</t>
@@ -227,7 +233,7 @@
     <t>Ageing Navigator provides practical next steps, questions and support pathways. It does not diagnose dementia and does not replace assessment by a health professional.</t>
   </si>
   <si>
-    <t>trigger has dementia_diagnosis or q8 has memory_or_thinking or q8 has changes_in_behaviour_or_personality or q9 has memory_or_thinking_has_changed or q9 has behaviour_or_personality_has_changed or q17 has memory_problems or q17 has becoming_lost_or_disorientated</t>
+    <t>trigger is dementia_diagnosis or q8 has memory_or_thinking or q8 has changes_in_behaviour_or_personality or q9 has memory_or_thinking_has_changed or q9 has behaviour_or_personality_has_changed or q17 has memory_problems or q17 has becoming_lost_or_disorientated</t>
   </si>
   <si>
     <t>s5</t>
@@ -269,7 +275,7 @@
     <t>Where village information exists in our repository, your plan may show options that appear to match your answers, with the reason for each match. Providers cannot pay to be ranked higher.</t>
   </si>
   <si>
-    <t>trigger has considering_village or q23 in village, serviced, planning_move or q8 has retirement_villages or q6 in village_independent, village_serviced</t>
+    <t>trigger is considering_village or q23 in village, serviced, planning_move or q8 has retirement_villages or q6 in village_independent, village_serviced</t>
   </si>
   <si>
     <t>residential</t>
@@ -281,7 +287,7 @@
     <t>Ageing Navigator never determines the level of residential care. Where a formal assessment has identified a level, we record what you tell us.</t>
   </si>
   <si>
-    <t>trigger has considering_residential or q23 is residential_care or q8 has residential_care or q6 is residential_care</t>
+    <t>trigger is considering_residential or q23 is residential_care or q8 has residential_care or q6 is residential_care</t>
   </si>
   <si>
     <t>s8</t>
@@ -335,40 +341,30 @@
     <t>trigger</t>
   </si>
   <si>
-    <t>Multiple choice</t>
-  </si>
-  <si>
-    <t>What has changed, or what is prompting you to look for help?</t>
-  </si>
-  <si>
-    <t>Choose everything that applies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dementia_diagnosis = A new dementia diagnosis
-stroke = A stroke
-hospital = A hospital admission or discharge
-fall = A fall
-mobility = Increasing mobility problems
-support_needs = Increasing support needs
-managing_home = Managing the home is becoming difficult
-carer_change = A spouse or carer can no longer give the same support
-considering_village = Considering retirement living
-considering_residential = Considering residential care
-planning_ahead = Planning ahead
-not_sure = I'm not sure what we need
-other = Something else</t>
-  </si>
-  <si>
-    <t>not_sure</t>
+    <t>Single choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dementia_diagnosis = A dementia diagnosis | Recently diagnosed or concerns about memory changes.
+hospital = A hospital admission or discharge | Planning the next steps after a hospital stay.
+fall_stroke_mobility = A fall, stroke or change in mobility | Recovering from a fall or noticing changes in mobility.
+managing_home = Managing at home is getting harder | Daily tasks are becoming more difficult.
+carer_change = A partner or family carer is struggling | The person providing support is finding it harder to manage.
+support_needs = Support or care needs are increasing | More help may be needed now or soon.
+respite = You need respite or a break from caring | A family carer needs a break, or temporary care is needed for a short period.
+considering_village = You're considering a retirement village | Exploring retirement living options.
+considering_residential = You're exploring residential care | Considering a care home because support needs are increasing.
+epoa = You want to organise an EPOA | You want to put an Enduring Power of Attorney in place or understand what needs to happen next.
+planning_ahead = You want to plan ahead | Thinking about the future even if there are no immediate changes.
+not_sure = I'm simply not sure | I don’t know where to start.</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
+    <t>2026-10-13: single choice, as the cards on the client's website (ageingnavigator.com). Was multiple choice with 13 options; fall, stroke and mobility merged; respite and epoa added; other removed.</t>
+  </si>
+  <si>
     <t>q1</t>
-  </si>
-  <si>
-    <t>Single choice</t>
   </si>
   <si>
     <t>How are you completing this questionnaire?</t>
@@ -484,6 +480,9 @@
   </si>
   <si>
     <t>q8</t>
+  </si>
+  <si>
+    <t>Multiple choice</t>
   </si>
   <si>
     <t>What are you currently concerned about?</t>
@@ -645,6 +644,9 @@
 not_sure = Not sure</t>
   </si>
   <si>
+    <t>not_sure</t>
+  </si>
+  <si>
     <t>q12</t>
   </si>
   <si>
@@ -1404,7 +1406,7 @@
     <t>Retirement village</t>
   </si>
   <si>
-    <t>q23 in village, serviced, planning_move or trigger has considering_village or q8 has retirement_villages</t>
+    <t>q23 in village, serviced, planning_move or trigger is considering_village or q8 has retirement_villages</t>
   </si>
   <si>
     <t>A retirement village is being considered. This is a possible pathway to investigate: which villages fit what matters to {{name}}, what care is available on site, and what the contracts involve.</t>
@@ -1416,7 +1418,7 @@
     <t>{{name}} already lives in residential care. A possible pathway to investigate is whether the current care still meets their needs. Any change in the level of care is decided through a formal needs assessment, not by Ageing Navigator.</t>
   </si>
   <si>
-    <t>q23 is residential_care or trigger has considering_residential or q8 has residential_care or q6 is residential_care</t>
+    <t>q23 is residential_care or trigger is considering_residential or q8 has residential_care or q6 is residential_care</t>
   </si>
   <si>
     <t>Residential care is being considered. This is a possible pathway to investigate. The level of care someone needs is decided through a formal needs assessment, not by Ageing Navigator.</t>
@@ -1485,7 +1487,7 @@
     <t>trigger answered</t>
   </si>
   <si>
-    <t>What has changed: {{answer.trigger}}.</t>
+    <t>What brought you here: {{answer.trigger}}.</t>
   </si>
   <si>
     <t>summary-8</t>
@@ -1814,7 +1816,7 @@
     <t>Falls and mobility</t>
   </si>
   <si>
-    <t>q17_falls in one, two_three, more or q17 has falling or q8 has falls or trigger has fall</t>
+    <t>q17_falls in one, two_three, more or q17 has falling or q8 has falls or trigger is fall_stroke_mobility</t>
   </si>
   <si>
     <t>Talk to the GP about falls and ask about strength and balance classes</t>
@@ -1930,7 +1932,7 @@
     <t>dementia-support</t>
   </si>
   <si>
-    <t>m1 in diagnosed, being_assessed or trigger has dementia_diagnosis</t>
+    <t>m1 in diagnosed, being_assessed or trigger is dementia_diagnosis</t>
   </si>
   <si>
     <t>Contact local dementia support services</t>
@@ -1976,7 +1978,7 @@
     <t>Family carer</t>
   </si>
   <si>
-    <t>q16 in significant, some or q9 has an_unpaid_family_carer_is_struggling</t>
+    <t>q16 in significant, some or q9 has an_unpaid_family_carer_is_struggling or trigger in carer_change, respite</t>
   </si>
   <si>
     <t>Get support for the family carer</t>
@@ -2001,7 +2003,7 @@
     <t>respite</t>
   </si>
   <si>
-    <t>q16 is significant or q8 has respite</t>
+    <t>q16 is significant or q8 has respite or trigger is respite</t>
   </si>
   <si>
     <t>Find out about respite options</t>
@@ -2032,7 +2034,7 @@
     <t>Legal</t>
   </si>
   <si>
-    <t>q21.epoa_property in no, unsure or q21.epoa_welfare in no, unsure</t>
+    <t>q21.epoa_property in no, unsure or q21.epoa_welfare in no, unsure or trigger is epoa</t>
   </si>
   <si>
     <t>Set up or check the Enduring Powers of Attorney</t>
@@ -2233,7 +2235,7 @@
     <t>residential-assessment</t>
   </si>
   <si>
-    <t>(q23 is residential_care or trigger has considering_residential or q8 has residential_care or q6 is residential_care) and (q19_level not answered or q19_level in none, unsure, home_support)</t>
+    <t>(q23 is residential_care or trigger is considering_residential or q8 has residential_care or q6 is residential_care) and (q19_level not answered or q19_level in none, unsure, home_support)</t>
   </si>
   <si>
     <t>Ask how an assessment for residential care is arranged</t>
@@ -2287,7 +2289,7 @@
     <t>residential-funding</t>
   </si>
   <si>
-    <t>(q23 is residential_care or trigger has considering_residential or q8 has residential_care or q6 is residential_care) and (q20 in very_important, important or rc3 has any government_funding, costs)</t>
+    <t>(q23 is residential_care or trigger is considering_residential or q8 has residential_care or q6 is residential_care) and (q20 in very_important, important or rc3 has any government_funding, costs)</t>
   </si>
   <si>
     <t>Find out about the Residential Care Subsidy and Loan</t>
@@ -2343,7 +2345,7 @@
     <t>Planning ahead</t>
   </si>
   <si>
-    <t>q23 in not_discussed, family_differs, unsure, open or trigger has planning_ahead</t>
+    <t>q23 in not_discussed, family_differs, unsure, open or trigger is planning_ahead</t>
   </si>
   <si>
     <t>Talk with {{name}} about wishes for the future</t>
@@ -2836,7 +2838,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E5F"/>
+        <fgColor rgb="FF174A4B"/>
       </patternFill>
     </fill>
   </fills>
@@ -3199,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -3394,14 +3396,22 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3422,54 +3432,54 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3495,342 +3505,342 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -3850,26 +3860,26 @@
   <sheetData>
     <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3891,27 +3901,27 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>1</v>
@@ -3919,10 +3929,10 @@
     </row>
     <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
@@ -3933,10 +3943,10 @@
     </row>
     <row r="4" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>1</v>
@@ -3947,24 +3957,24 @@
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>1</v>
@@ -3975,10 +3985,10 @@
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>1</v>
@@ -3989,24 +3999,24 @@
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>1</v>
@@ -4017,24 +4027,24 @@
     </row>
     <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>1</v>
@@ -4045,10 +4055,10 @@
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>1</v>
@@ -4059,38 +4069,38 @@
     </row>
     <row r="13" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>1</v>
@@ -4101,10 +4111,10 @@
     </row>
     <row r="16" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>1</v>
@@ -4115,10 +4125,10 @@
     </row>
     <row r="17" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>1</v>
@@ -4149,90 +4159,90 @@
   <sheetData>
     <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="J1" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>107</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -4240,23 +4250,23 @@
         <v>110</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="H3" s="4" t="s">
         <v>1</v>
       </c>
@@ -4264,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>1</v>
@@ -4281,43 +4291,43 @@
     </row>
     <row r="4" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>117</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>1</v>
@@ -4325,26 +4335,26 @@
     </row>
     <row r="5" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="H5" s="4" t="s">
         <v>1</v>
       </c>
@@ -4352,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>1</v>
@@ -4369,26 +4379,26 @@
     </row>
     <row r="6" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="H6" s="4" t="s">
         <v>1</v>
       </c>
@@ -4396,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>1</v>
@@ -4413,23 +4423,23 @@
     </row>
     <row r="7" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="G7" s="4" t="s">
         <v>1</v>
       </c>
@@ -4440,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>1</v>
@@ -4457,23 +4467,23 @@
     </row>
     <row r="8" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="G8" s="4" t="s">
         <v>1</v>
       </c>
@@ -4484,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>1</v>
@@ -4501,26 +4511,26 @@
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="H9" s="4" t="s">
         <v>1</v>
       </c>
@@ -4528,7 +4538,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>1</v>
@@ -4545,26 +4555,26 @@
     </row>
     <row r="10" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="H10" s="4" t="s">
         <v>1</v>
       </c>
@@ -4572,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>1</v>
@@ -4589,16 +4599,16 @@
     </row>
     <row r="11" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>138</v>
@@ -4616,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>1</v>
@@ -4636,13 +4646,13 @@
         <v>142</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>143</v>
@@ -4660,7 +4670,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>1</v>
@@ -4680,7 +4690,7 @@
         <v>146</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>1</v>
@@ -4724,13 +4734,13 @@
         <v>151</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>152</v>
@@ -4748,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>1</v>
@@ -4768,13 +4778,13 @@
         <v>154</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>155</v>
@@ -4812,13 +4822,13 @@
         <v>157</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>158</v>
@@ -4836,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>1</v>
@@ -4856,13 +4866,13 @@
         <v>160</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>161</v>
@@ -4880,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>1</v>
@@ -4900,13 +4910,13 @@
         <v>164</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>165</v>
@@ -4918,13 +4928,13 @@
         <v>166</v>
       </c>
       <c r="H18" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>1</v>
@@ -4941,34 +4951,34 @@
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>1</v>
@@ -4985,25 +4995,25 @@
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>1</v>
@@ -5012,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>1</v>
@@ -5029,34 +5039,34 @@
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>1</v>
@@ -5073,25 +5083,25 @@
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>1</v>
@@ -5100,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>1</v>
@@ -5117,25 +5127,25 @@
     </row>
     <row r="23" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>1</v>
@@ -5144,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>1</v>
@@ -5161,22 +5171,22 @@
     </row>
     <row r="24" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>1</v>
@@ -5197,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N24" s="4" t="s">
         <v>1</v>
@@ -5205,34 +5215,34 @@
     </row>
     <row r="25" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>1</v>
@@ -5249,25 +5259,25 @@
     </row>
     <row r="26" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>1</v>
@@ -5276,7 +5286,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>1</v>
@@ -5293,25 +5303,25 @@
     </row>
     <row r="27" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>1</v>
@@ -5320,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>1</v>
@@ -5337,25 +5347,25 @@
     </row>
     <row r="28" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>1</v>
@@ -5373,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>1</v>
@@ -5381,10 +5391,10 @@
     </row>
     <row r="29" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>1</v>
@@ -5393,7 +5403,7 @@
         <v>147</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1</v>
@@ -5417,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>1</v>
@@ -5425,16 +5435,16 @@
     </row>
     <row r="30" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>158</v>
@@ -5443,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>1</v>
@@ -5452,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>1</v>
@@ -5469,34 +5479,34 @@
     </row>
     <row r="31" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>1</v>
@@ -5513,25 +5523,25 @@
     </row>
     <row r="32" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>1</v>
@@ -5540,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>1</v>
@@ -5557,25 +5567,25 @@
     </row>
     <row r="33" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>1</v>
@@ -5584,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>1</v>
@@ -5593,7 +5603,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N33" s="4" t="s">
         <v>1</v>
@@ -5601,25 +5611,25 @@
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>1</v>
@@ -5628,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>1</v>
@@ -5645,25 +5655,25 @@
     </row>
     <row r="35" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>1</v>
@@ -5672,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>1</v>
@@ -5689,25 +5699,25 @@
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>1</v>
@@ -5716,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>1</v>
@@ -5733,25 +5743,25 @@
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>1</v>
@@ -5760,7 +5770,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>1</v>
@@ -5777,25 +5787,25 @@
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>1</v>
@@ -5804,13 +5814,13 @@
         <v>1</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>1</v>
@@ -5821,25 +5831,25 @@
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>1</v>
@@ -5848,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>1</v>
@@ -5865,25 +5875,25 @@
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>1</v>
@@ -5892,7 +5902,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>1</v>
@@ -5909,34 +5919,34 @@
     </row>
     <row r="41" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>1</v>
@@ -5953,25 +5963,25 @@
     </row>
     <row r="42" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>1</v>
@@ -5980,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>1</v>
@@ -5997,19 +6007,19 @@
     </row>
     <row r="43" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>1</v>
@@ -6024,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>1</v>
@@ -6033,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>1</v>
@@ -6041,25 +6051,25 @@
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>1</v>
@@ -6068,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>1</v>
@@ -6085,25 +6095,25 @@
     </row>
     <row r="45" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>1</v>
@@ -6112,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>1</v>
@@ -6129,25 +6139,25 @@
     </row>
     <row r="46" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>1</v>
@@ -6156,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>1</v>
@@ -6173,34 +6183,34 @@
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H47" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>1</v>
@@ -6217,25 +6227,25 @@
     </row>
     <row r="48" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>1</v>
@@ -6244,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>1</v>
@@ -6261,25 +6271,25 @@
     </row>
     <row r="49" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>1</v>
@@ -6288,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>1</v>
@@ -6305,16 +6315,16 @@
     </row>
     <row r="50" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>158</v>
@@ -6323,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>1</v>
@@ -6332,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>1</v>
@@ -6349,34 +6359,34 @@
     </row>
     <row r="51" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H51" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J51" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>1</v>
@@ -6393,25 +6403,25 @@
     </row>
     <row r="52" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>1</v>
@@ -6420,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>1</v>
@@ -6437,25 +6447,25 @@
     </row>
     <row r="53" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>1</v>
@@ -6464,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>1</v>
@@ -6481,34 +6491,34 @@
     </row>
     <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>1</v>
@@ -6525,25 +6535,25 @@
     </row>
     <row r="55" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>1</v>
@@ -6552,7 +6562,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>1</v>
@@ -6569,34 +6579,34 @@
     </row>
     <row r="56" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>1</v>
@@ -6613,10 +6623,10 @@
     </row>
     <row r="57" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>1</v>
@@ -6625,10 +6635,10 @@
         <v>147</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1</v>
@@ -6657,34 +6667,34 @@
     </row>
     <row r="58" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>139</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>1</v>
@@ -6701,37 +6711,37 @@
     </row>
     <row r="59" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>1</v>
@@ -6745,10 +6755,10 @@
     </row>
     <row r="60" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>1</v>
@@ -6757,7 +6767,7 @@
         <v>147</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>1</v>
@@ -6960,104 +6970,104 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7281,291 +7291,291 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7783,280 +7793,280 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>163</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>402</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>1</v>
@@ -8065,162 +8075,162 @@
         <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>1</v>
@@ -8229,121 +8239,121 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>485</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>1</v>
@@ -8352,156 +8362,156 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -8510,39 +8520,39 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -8554,36 +8564,36 @@
         <v>1</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>1</v>
@@ -8595,36 +8605,36 @@
         <v>1</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -8636,282 +8646,282 @@
         <v>1</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>576</v>
-      </c>
       <c r="M24" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>1</v>
@@ -8926,33 +8936,33 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>1</v>
@@ -8967,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -9175,209 +9185,209 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="7:7" x14ac:dyDescent="0.25"/>
@@ -9596,210 +9606,210 @@
   <sheetData>
     <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="773">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -344,24 +344,20 @@
     <t>Single choice</t>
   </si>
   <si>
-    <t xml:space="preserve">dementia_diagnosis = A dementia diagnosis | Recently diagnosed or concerns about memory changes.
+    <t xml:space="preserve">dementia_diagnosis = Dementia diagnosis or memory concerns | Recently diagnosed or concerns about memory changes.
 hospital = A hospital admission or discharge | Planning the next steps after a hospital stay.
 fall_stroke_mobility = A fall, stroke or change in mobility | Recovering from a fall or noticing changes in mobility.
-managing_home = Managing at home is getting harder | Daily tasks are becoming more difficult.
-carer_change = A partner or family carer is struggling | The person providing support is finding it harder to manage.
-support_needs = Support or care needs are increasing | More help may be needed now or soon.
-respite = You need respite or a break from caring | A family carer needs a break, or temporary care is needed for a short period.
+managing_home = Managing at home is getting harder | Daily tasks are getting harder, or more help may be needed now or soon.
+carer_change = Caring is becoming too much | The person providing support is finding it hard to manage, or needs a break.
 considering_village = You're considering a retirement village | Exploring retirement living options.
 considering_residential = You're exploring residential care | Considering a care home because support needs are increasing.
-epoa = You want to organise an EPOA | You want to put an Enduring Power of Attorney in place or understand what needs to happen next.
-planning_ahead = You want to plan ahead | Thinking about the future even if there are no immediate changes.
-not_sure = I'm simply not sure | I don’t know where to start.</t>
+what_next = You want help understanding what to do next | Planning ahead, or not sure where to start.</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>2026-10-13: single choice, as the cards on the client's website (ageingnavigator.com). Was multiple choice with 13 options; fall, stroke and mobility merged; respite and epoa added; other removed.</t>
+    <t>2026-10-13: single choice, as the cards on the client's website (ageingnavigator.com). Was multiple choice with 13 options; fall, stroke and mobility merged; respite and epoa added; other removed. 2026-10-13: 8 cards (support needs merged into managing at home; respite into caring; planning ahead and not sure into what_next; EPOA card removed).</t>
   </si>
   <si>
     <t>q1</t>
@@ -444,10 +440,16 @@
     <t>q5_region</t>
   </si>
   <si>
+    <t>Drop-down</t>
+  </si>
+  <si>
     <t>Which region?</t>
   </si>
   <si>
-    <t>For example Canterbury, Wellington or Nelson.</t>
+    <t>The pilot covers the Bay of Plenty for now.</t>
+  </si>
+  <si>
+    <t>bay_of_plenty = Bay of Plenty</t>
   </si>
   <si>
     <t>q6</t>
@@ -1978,7 +1980,7 @@
     <t>Family carer</t>
   </si>
   <si>
-    <t>q16 in significant, some or q9 has an_unpaid_family_carer_is_struggling or trigger in carer_change, respite</t>
+    <t>q16 in significant, some or q9 has an_unpaid_family_carer_is_struggling or trigger is carer_change</t>
   </si>
   <si>
     <t>Get support for the family carer</t>
@@ -2003,7 +2005,7 @@
     <t>respite</t>
   </si>
   <si>
-    <t>q16 is significant or q8 has respite or trigger is respite</t>
+    <t>q16 is significant or q8 has respite or trigger is carer_change</t>
   </si>
   <si>
     <t>Find out about respite options</t>
@@ -2034,7 +2036,7 @@
     <t>Legal</t>
   </si>
   <si>
-    <t>q21.epoa_property in no, unsure or q21.epoa_welfare in no, unsure or trigger is epoa</t>
+    <t>q21.epoa_property in no, unsure or q21.epoa_welfare in no, unsure</t>
   </si>
   <si>
     <t>Set up or check the Enduring Powers of Attorney</t>
@@ -2345,7 +2347,7 @@
     <t>Planning ahead</t>
   </si>
   <si>
-    <t>q23 in not_discussed, family_differs, unsure, open or trigger is planning_ahead</t>
+    <t>q23 in not_discussed, family_differs, unsure, open or trigger is what_next</t>
   </si>
   <si>
     <t>Talk with {{name}} about wishes for the future</t>
@@ -2471,7 +2473,7 @@
     <t>consent</t>
   </si>
   <si>
-    <t>Ageing Navigator will use your answers to prepare a personalised Family Ageing Action Plan. A navigator checks every plan before it is sent to you. Your answers are stored securely in Australia, seen only by the Ageing Navigator team, and deleted 12 months after your plan is sent, or sooner if you ask. We do not use AI, and we do not share your answers with anyone else without asking you first.</t>
+    <t>Ageing Navigator will use your answers to prepare a personalised Family Ageing Action Plan, which you receive as soon as you finish. Your answers are stored securely in Australia, seen only by the Ageing Navigator team, and deleted 12 months after your plan is sent, or sooner if you ask. We do not use AI, and we do not share your answers with anyone else without asking you first.</t>
   </si>
   <si>
     <t>consent_checkbox</t>
@@ -2483,7 +2485,7 @@
     <t>thank_you</t>
   </si>
   <si>
-    <t>Thank you. Your answers have reached Ageing Navigator. A navigator will check your personalised Action Plan and email it to you, usually within a few working days.</t>
+    <t>Thank you. Your personalised Family Ageing Action Plan is ready. We have also emailed you a private link to it, so you can come back to it at any time.</t>
   </si>
   <si>
     <t>urgent_guidance</t>
@@ -2519,7 +2521,7 @@
     <t>cta_default</t>
   </si>
   <si>
-    <t>Would you like Ageing Navigator to organise these next steps for you?</t>
+    <t>Would you like Ageing Navigator to help coordinate everything? For the first 10 families, this is free.</t>
   </si>
   <si>
     <t>email_release_subject</t>
@@ -2532,16 +2534,16 @@
   </si>
   <si>
     <t xml:space="preserve">Hello,
-Your personalised Family Ageing Action Plan has been checked by a navigator and is ready.
+Your personalised Family Ageing Action Plan is ready.
 Open your plan: {{link}}
-This link is private to you. It works until {{expires}}. On the plan page you can download it as a PDF, and ask us for help with any of the steps.
+This link is private to you. It works until {{expires}}. On the plan page you can download it as a PDF, and ask us to help coordinate any of the steps.
 Ageing Navigator</t>
   </si>
   <si>
     <t>request_intro</t>
   </si>
   <si>
-    <t>Tell us what you would like help with and a navigator will contact you to talk it through. There is no obligation, and we will tell you the cost before anything starts.</t>
+    <t>Tell us what you would like help with, and a navigator will contact you to talk it through. There is no obligation.</t>
   </si>
   <si>
     <t>request_done</t>
@@ -2565,19 +2567,19 @@
     <t>cta_stay_home</t>
   </si>
   <si>
-    <t>Would you like Ageing Navigator to organise your Home Support Setup?</t>
+    <t>Would you like Ageing Navigator to help coordinate support at home? For the first 10 families, this is free.</t>
   </si>
   <si>
     <t>cta_village</t>
   </si>
   <si>
-    <t>Would you like Ageing Navigator to help coordinate your Retirement Village Transition?</t>
+    <t>Would you like Ageing Navigator to help coordinate a move to a retirement village? For the first 10 families, this is free.</t>
   </si>
   <si>
     <t>cta_residential</t>
   </si>
   <si>
-    <t>Would you like Ageing Navigator to search for and coordinate Residential Care?</t>
+    <t>Would you like Ageing Navigator to help coordinate finding residential care? For the first 10 families, this is free.</t>
   </si>
   <si>
     <t>feedback_intro</t>
@@ -2613,19 +2615,19 @@
     <t>home_support_setup</t>
   </si>
   <si>
-    <t>Home Support Setup</t>
+    <t>Home support: search and coordination</t>
   </si>
   <si>
     <t>village_transition</t>
   </si>
   <si>
-    <t>Retirement Village Transition</t>
+    <t>Retirement village: search and coordination</t>
   </si>
   <si>
     <t>residential_transition</t>
   </si>
   <si>
-    <t>Residential Care Search and Transition</t>
+    <t>Residential care: search and coordination</t>
   </si>
   <si>
     <t>something_else</t>
@@ -3435,7 +3437,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>96</v>
@@ -3443,21 +3445,21 @@
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>81</v>
@@ -3465,10 +3467,10 @@
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>85</v>
@@ -3476,10 +3478,10 @@
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3511,336 +3513,336 @@
         <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>633</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>722</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>734</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -4476,16 +4478,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>1</v>
@@ -4511,7 +4513,7 @@
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>56</v>
@@ -4523,13 +4525,13 @@
         <v>106</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>1</v>
@@ -4555,7 +4557,7 @@
     </row>
     <row r="10" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>56</v>
@@ -4567,13 +4569,13 @@
         <v>106</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>1</v>
@@ -4599,7 +4601,7 @@
     </row>
     <row r="11" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>58</v>
@@ -4608,19 +4610,19 @@
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>1</v>
@@ -4643,7 +4645,7 @@
     </row>
     <row r="12" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>58</v>
@@ -4652,19 +4654,19 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>1</v>
@@ -4687,7 +4689,7 @@
     </row>
     <row r="13" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>58</v>
@@ -4696,13 +4698,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>1</v>
@@ -4714,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>1</v>
@@ -4731,7 +4733,7 @@
     </row>
     <row r="14" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>58</v>
@@ -4743,13 +4745,13 @@
         <v>106</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>1</v>
@@ -4775,7 +4777,7 @@
     </row>
     <row r="15" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>58</v>
@@ -4787,7 +4789,7 @@
         <v>124</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>1</v>
@@ -4802,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>1</v>
@@ -4811,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>1</v>
@@ -4819,7 +4821,7 @@
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>60</v>
@@ -4831,13 +4833,13 @@
         <v>106</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>1</v>
@@ -4863,7 +4865,7 @@
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>60</v>
@@ -4875,13 +4877,13 @@
         <v>106</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>1</v>
@@ -4899,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>1</v>
@@ -4907,7 +4909,7 @@
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>60</v>
@@ -4916,19 +4918,19 @@
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -4951,7 +4953,7 @@
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>63</v>
@@ -4960,19 +4962,19 @@
         <v>1</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -4995,7 +4997,7 @@
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>63</v>
@@ -5007,13 +5009,13 @@
         <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>1</v>
@@ -5039,7 +5041,7 @@
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>63</v>
@@ -5048,19 +5050,19 @@
         <v>1</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -5083,7 +5085,7 @@
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>63</v>
@@ -5095,13 +5097,13 @@
         <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>1</v>
@@ -5127,7 +5129,7 @@
     </row>
     <row r="23" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>63</v>
@@ -5139,13 +5141,13 @@
         <v>106</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>1</v>
@@ -5171,7 +5173,7 @@
     </row>
     <row r="24" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>63</v>
@@ -5183,10 +5185,10 @@
         <v>124</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>1</v>
@@ -5198,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>1</v>
@@ -5207,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N24" s="4" t="s">
         <v>1</v>
@@ -5215,7 +5217,7 @@
     </row>
     <row r="25" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>65</v>
@@ -5224,19 +5226,19 @@
         <v>1</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
@@ -5259,7 +5261,7 @@
     </row>
     <row r="26" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>65</v>
@@ -5271,13 +5273,13 @@
         <v>106</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>1</v>
@@ -5303,7 +5305,7 @@
     </row>
     <row r="27" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>65</v>
@@ -5315,13 +5317,13 @@
         <v>106</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>1</v>
@@ -5356,16 +5358,16 @@
         <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>1</v>
@@ -5374,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>1</v>
@@ -5383,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>1</v>
@@ -5391,7 +5393,7 @@
     </row>
     <row r="29" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>65</v>
@@ -5400,10 +5402,10 @@
         <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1</v>
@@ -5418,7 +5420,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>1</v>
@@ -5427,7 +5429,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>1</v>
@@ -5435,7 +5437,7 @@
     </row>
     <row r="30" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>67</v>
@@ -5447,13 +5449,13 @@
         <v>106</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>1</v>
@@ -5479,7 +5481,7 @@
     </row>
     <row r="31" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>67</v>
@@ -5488,22 +5490,22 @@
         <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>108</v>
@@ -5523,7 +5525,7 @@
     </row>
     <row r="32" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>71</v>
@@ -5535,13 +5537,13 @@
         <v>106</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>1</v>
@@ -5567,7 +5569,7 @@
     </row>
     <row r="33" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>71</v>
@@ -5579,13 +5581,13 @@
         <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>1</v>
@@ -5603,7 +5605,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N33" s="4" t="s">
         <v>1</v>
@@ -5611,7 +5613,7 @@
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>71</v>
@@ -5623,13 +5625,13 @@
         <v>106</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>1</v>
@@ -5655,7 +5657,7 @@
     </row>
     <row r="35" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>73</v>
@@ -5667,13 +5669,13 @@
         <v>106</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>1</v>
@@ -5699,7 +5701,7 @@
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>73</v>
@@ -5711,13 +5713,13 @@
         <v>106</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>1</v>
@@ -5743,7 +5745,7 @@
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>73</v>
@@ -5755,13 +5757,13 @@
         <v>106</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>1</v>
@@ -5787,7 +5789,7 @@
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>77</v>
@@ -5796,16 +5798,16 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>1</v>
@@ -5820,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>1</v>
@@ -5831,7 +5833,7 @@
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>77</v>
@@ -5843,13 +5845,13 @@
         <v>106</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>1</v>
@@ -5875,7 +5877,7 @@
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>79</v>
@@ -5887,13 +5889,13 @@
         <v>106</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>1</v>
@@ -5919,7 +5921,7 @@
     </row>
     <row r="41" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>79</v>
@@ -5928,19 +5930,19 @@
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>1</v>
@@ -5963,7 +5965,7 @@
     </row>
     <row r="42" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>81</v>
@@ -5975,13 +5977,13 @@
         <v>106</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>1</v>
@@ -6007,7 +6009,7 @@
     </row>
     <row r="43" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>81</v>
@@ -6019,7 +6021,7 @@
         <v>124</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>1</v>
@@ -6043,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>1</v>
@@ -6051,7 +6053,7 @@
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>81</v>
@@ -6060,16 +6062,16 @@
         <v>81</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>1</v>
@@ -6095,7 +6097,7 @@
     </row>
     <row r="45" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>81</v>
@@ -6107,13 +6109,13 @@
         <v>106</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>1</v>
@@ -6139,7 +6141,7 @@
     </row>
     <row r="46" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>81</v>
@@ -6151,13 +6153,13 @@
         <v>106</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>1</v>
@@ -6183,7 +6185,7 @@
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>81</v>
@@ -6192,19 +6194,19 @@
         <v>81</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>1</v>
@@ -6227,7 +6229,7 @@
     </row>
     <row r="48" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>81</v>
@@ -6239,13 +6241,13 @@
         <v>106</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>1</v>
@@ -6271,7 +6273,7 @@
     </row>
     <row r="49" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>81</v>
@@ -6283,13 +6285,13 @@
         <v>106</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>1</v>
@@ -6315,7 +6317,7 @@
     </row>
     <row r="50" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>85</v>
@@ -6327,13 +6329,13 @@
         <v>106</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>1</v>
@@ -6359,7 +6361,7 @@
     </row>
     <row r="51" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>85</v>
@@ -6368,19 +6370,19 @@
         <v>85</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>1</v>
@@ -6403,7 +6405,7 @@
     </row>
     <row r="52" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>89</v>
@@ -6415,13 +6417,13 @@
         <v>106</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>1</v>
@@ -6447,7 +6449,7 @@
     </row>
     <row r="53" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>89</v>
@@ -6459,13 +6461,13 @@
         <v>106</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>1</v>
@@ -6491,7 +6493,7 @@
     </row>
     <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>89</v>
@@ -6503,19 +6505,19 @@
         <v>106</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>108</v>
@@ -6535,7 +6537,7 @@
     </row>
     <row r="55" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>89</v>
@@ -6547,13 +6549,13 @@
         <v>106</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>1</v>
@@ -6579,7 +6581,7 @@
     </row>
     <row r="56" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>91</v>
@@ -6588,19 +6590,19 @@
         <v>1</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>1</v>
@@ -6623,7 +6625,7 @@
     </row>
     <row r="57" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>91</v>
@@ -6632,13 +6634,13 @@
         <v>1</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1</v>
@@ -6650,7 +6652,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>1</v>
@@ -6667,7 +6669,7 @@
     </row>
     <row r="58" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>93</v>
@@ -6676,22 +6678,22 @@
         <v>1</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>108</v>
@@ -6711,7 +6713,7 @@
     </row>
     <row r="59" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>93</v>
@@ -6720,28 +6722,28 @@
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>108</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>1</v>
@@ -6755,7 +6757,7 @@
     </row>
     <row r="60" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>93</v>
@@ -6764,10 +6766,10 @@
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>1</v>
@@ -6782,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>1</v>
@@ -6940,10 +6942,10 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="D10:D200">
-      <formula1>"Single choice,Multiple choice,Short text,Long text,Grid"</formula1>
+      <formula1>"Single choice,Drop-down,Multiple choice,Short text,Long text,Grid"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D200">
-      <formula1>"Single choice,Multiple choice,Short text,Long text,Grid"</formula1>
+      <formula1>"Single choice,Drop-down,Multiple choice,Short text,Long text,Grid"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="J10:J200">
       <formula1>"yes,no"</formula1>
@@ -6973,50 +6975,50 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7024,16 +7026,16 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7044,13 +7046,13 @@
         <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7061,13 +7063,13 @@
         <v>86</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7300,282 +7302,282 @@
         <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7796,277 +7798,277 @@
         <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>1</v>
@@ -8075,162 +8077,162 @@
         <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>1</v>
@@ -8239,121 +8241,121 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>486</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>1</v>
@@ -8362,156 +8364,156 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -8520,39 +8522,39 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -8564,36 +8566,36 @@
         <v>1</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>1</v>
@@ -8605,36 +8607,36 @@
         <v>1</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -8646,282 +8648,282 @@
         <v>1</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>403</v>
-      </c>
       <c r="M22" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>579</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>577</v>
-      </c>
       <c r="M24" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>1</v>
@@ -8936,33 +8938,33 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>1</v>
@@ -8977,7 +8979,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -9197,197 +9199,197 @@
         <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="7:7" x14ac:dyDescent="0.25"/>
@@ -9609,207 +9611,207 @@
         <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="778">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -425,31 +425,37 @@
 unsure = Not sure</t>
   </si>
   <si>
+    <t>q5_region</t>
+  </si>
+  <si>
+    <t>Drop-down</t>
+  </si>
+  <si>
+    <t>Which region?</t>
+  </si>
+  <si>
+    <t>The pilot covers the Bay of Plenty for now.</t>
+  </si>
+  <si>
+    <t>bay_of_plenty = Bay of Plenty</t>
+  </si>
+  <si>
     <t>q5_town</t>
   </si>
   <si>
-    <t>Short text</t>
-  </si>
-  <si>
-    <t>Which town or city do they live in?</t>
-  </si>
-  <si>
-    <t>Town or city and region only.</t>
-  </si>
-  <si>
-    <t>q5_region</t>
-  </si>
-  <si>
-    <t>Drop-down</t>
-  </si>
-  <si>
-    <t>Which region?</t>
-  </si>
-  <si>
-    <t>The pilot covers the Bay of Plenty for now.</t>
-  </si>
-  <si>
-    <t>bay_of_plenty = Bay of Plenty</t>
+    <t>Which part of the Bay of Plenty do they live in?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tauranga = Tauranga (including Mount Maunganui, Pāpāmoa and Bethlehem)
+western_bay_of_plenty = Western Bay of Plenty (including Te Puke, Katikati and Ōmokoroa)
+whakatane = Whakatāne (including Ōhope)
+kawerau = Kawerau
+opotiki = Ōpōtiki
+rotorua = Rotorua
+somewhere_else = Somewhere else</t>
+  </si>
+  <si>
+    <t>2026-10-15: a drop-down of Bay of Plenty areas (was a free-text town), so care homes can be matched by area.</t>
   </si>
   <si>
     <t>q6</t>
@@ -585,6 +591,9 @@
     <t>q11a</t>
   </si>
   <si>
+    <t>Short text</t>
+  </si>
+  <si>
     <t>What decision or deadline are you dealing with?</t>
   </si>
   <si>
@@ -2607,6 +2616,18 @@
   </si>
   <si>
     <t>We only use these details to send the plan and to contact you about it.</t>
+  </si>
+  <si>
+    <t>care_homes_intro</t>
+  </si>
+  <si>
+    <t>These homes appear to match what you told us. This is not a recommendation, and Ageing Navigator receives no payment for listings. Please check availability, costs and suitability directly with each home.</t>
+  </si>
+  <si>
+    <t>care_homes_no_level</t>
+  </si>
+  <si>
+    <t>A needs assessment decides which level of care is needed, so the levels each home offers are shown.</t>
   </si>
   <si>
     <t>Label</t>
@@ -3437,7 +3458,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>96</v>
@@ -3445,21 +3466,21 @@
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>81</v>
@@ -3467,10 +3488,10 @@
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>85</v>
@@ -3478,10 +3499,10 @@
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3513,336 +3534,336 @@
         <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>727</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -4443,7 +4464,7 @@
         <v>126</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>1</v>
@@ -4469,7 +4490,7 @@
     </row>
     <row r="8" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>56</v>
@@ -4478,16 +4499,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>129</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>1</v>
@@ -4508,7 +4529,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -4786,10 +4807,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>1</v>
@@ -4813,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>1</v>
@@ -4821,7 +4842,7 @@
     </row>
     <row r="16" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>60</v>
@@ -4833,13 +4854,13 @@
         <v>106</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>1</v>
@@ -4865,7 +4886,7 @@
     </row>
     <row r="17" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>60</v>
@@ -4877,13 +4898,13 @@
         <v>106</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>1</v>
@@ -4901,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>1</v>
@@ -4909,7 +4930,7 @@
     </row>
     <row r="18" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>60</v>
@@ -4921,16 +4942,16 @@
         <v>139</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -4953,7 +4974,7 @@
     </row>
     <row r="19" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>63</v>
@@ -4965,16 +4986,16 @@
         <v>139</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -4997,7 +5018,7 @@
     </row>
     <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>63</v>
@@ -5009,13 +5030,13 @@
         <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>1</v>
@@ -5041,7 +5062,7 @@
     </row>
     <row r="21" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>63</v>
@@ -5053,16 +5074,16 @@
         <v>139</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -5085,7 +5106,7 @@
     </row>
     <row r="22" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>63</v>
@@ -5097,13 +5118,13 @@
         <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>1</v>
@@ -5129,7 +5150,7 @@
     </row>
     <row r="23" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>63</v>
@@ -5141,13 +5162,13 @@
         <v>106</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>1</v>
@@ -5173,7 +5194,7 @@
     </row>
     <row r="24" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>63</v>
@@ -5182,13 +5203,13 @@
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>1</v>
@@ -5209,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N24" s="4" t="s">
         <v>1</v>
@@ -5217,7 +5238,7 @@
     </row>
     <row r="25" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>65</v>
@@ -5229,16 +5250,16 @@
         <v>139</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
@@ -5261,7 +5282,7 @@
     </row>
     <row r="26" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>65</v>
@@ -5273,13 +5294,13 @@
         <v>106</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>1</v>
@@ -5305,7 +5326,7 @@
     </row>
     <row r="27" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>65</v>
@@ -5317,13 +5338,13 @@
         <v>106</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>1</v>
@@ -5361,13 +5382,13 @@
         <v>139</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>1</v>
@@ -5385,7 +5406,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>1</v>
@@ -5393,7 +5414,7 @@
     </row>
     <row r="29" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>65</v>
@@ -5405,7 +5426,7 @@
         <v>149</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1</v>
@@ -5429,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>1</v>
@@ -5437,7 +5458,7 @@
     </row>
     <row r="30" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>67</v>
@@ -5449,13 +5470,13 @@
         <v>106</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>1</v>
@@ -5481,7 +5502,7 @@
     </row>
     <row r="31" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>67</v>
@@ -5493,19 +5514,19 @@
         <v>139</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>108</v>
@@ -5525,7 +5546,7 @@
     </row>
     <row r="32" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>71</v>
@@ -5537,13 +5558,13 @@
         <v>106</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>1</v>
@@ -5569,7 +5590,7 @@
     </row>
     <row r="33" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>71</v>
@@ -5581,13 +5602,13 @@
         <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>1</v>
@@ -5605,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N33" s="4" t="s">
         <v>1</v>
@@ -5613,7 +5634,7 @@
     </row>
     <row r="34" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>71</v>
@@ -5625,13 +5646,13 @@
         <v>106</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>1</v>
@@ -5657,7 +5678,7 @@
     </row>
     <row r="35" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>73</v>
@@ -5669,13 +5690,13 @@
         <v>106</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>1</v>
@@ -5701,7 +5722,7 @@
     </row>
     <row r="36" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>73</v>
@@ -5713,13 +5734,13 @@
         <v>106</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>1</v>
@@ -5745,7 +5766,7 @@
     </row>
     <row r="37" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>73</v>
@@ -5757,13 +5778,13 @@
         <v>106</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>1</v>
@@ -5789,7 +5810,7 @@
     </row>
     <row r="38" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>77</v>
@@ -5798,16 +5819,16 @@
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>1</v>
@@ -5822,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M38" s="4" t="s">
         <v>1</v>
@@ -5833,7 +5854,7 @@
     </row>
     <row r="39" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>77</v>
@@ -5845,13 +5866,13 @@
         <v>106</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>1</v>
@@ -5877,7 +5898,7 @@
     </row>
     <row r="40" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>79</v>
@@ -5889,13 +5910,13 @@
         <v>106</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>1</v>
@@ -5921,7 +5942,7 @@
     </row>
     <row r="41" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>79</v>
@@ -5933,16 +5954,16 @@
         <v>139</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>1</v>
@@ -5965,7 +5986,7 @@
     </row>
     <row r="42" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>81</v>
@@ -5977,13 +5998,13 @@
         <v>106</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>1</v>
@@ -6009,7 +6030,7 @@
     </row>
     <row r="43" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>81</v>
@@ -6018,10 +6039,10 @@
         <v>81</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>1</v>
@@ -6045,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>1</v>
@@ -6053,7 +6074,7 @@
     </row>
     <row r="44" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>81</v>
@@ -6065,13 +6086,13 @@
         <v>139</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>1</v>
@@ -6097,7 +6118,7 @@
     </row>
     <row r="45" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>81</v>
@@ -6109,13 +6130,13 @@
         <v>106</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>1</v>
@@ -6141,7 +6162,7 @@
     </row>
     <row r="46" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>81</v>
@@ -6153,13 +6174,13 @@
         <v>106</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>1</v>
@@ -6185,7 +6206,7 @@
     </row>
     <row r="47" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>81</v>
@@ -6197,16 +6218,16 @@
         <v>139</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>1</v>
@@ -6229,7 +6250,7 @@
     </row>
     <row r="48" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>81</v>
@@ -6241,13 +6262,13 @@
         <v>106</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>1</v>
@@ -6273,7 +6294,7 @@
     </row>
     <row r="49" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>81</v>
@@ -6285,13 +6306,13 @@
         <v>106</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>1</v>
@@ -6317,7 +6338,7 @@
     </row>
     <row r="50" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>85</v>
@@ -6329,13 +6350,13 @@
         <v>106</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>1</v>
@@ -6361,7 +6382,7 @@
     </row>
     <row r="51" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>85</v>
@@ -6373,16 +6394,16 @@
         <v>139</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>1</v>
@@ -6405,7 +6426,7 @@
     </row>
     <row r="52" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>89</v>
@@ -6417,13 +6438,13 @@
         <v>106</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>1</v>
@@ -6449,7 +6470,7 @@
     </row>
     <row r="53" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>89</v>
@@ -6461,13 +6482,13 @@
         <v>106</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>1</v>
@@ -6493,7 +6514,7 @@
     </row>
     <row r="54" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>89</v>
@@ -6505,19 +6526,19 @@
         <v>106</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>108</v>
@@ -6537,7 +6558,7 @@
     </row>
     <row r="55" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>89</v>
@@ -6549,13 +6570,13 @@
         <v>106</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>1</v>
@@ -6581,7 +6602,7 @@
     </row>
     <row r="56" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>91</v>
@@ -6593,16 +6614,16 @@
         <v>139</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>1</v>
@@ -6625,7 +6646,7 @@
     </row>
     <row r="57" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>91</v>
@@ -6637,10 +6658,10 @@
         <v>149</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>1</v>
@@ -6669,7 +6690,7 @@
     </row>
     <row r="58" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>93</v>
@@ -6681,19 +6702,19 @@
         <v>139</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>141</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>108</v>
@@ -6713,7 +6734,7 @@
     </row>
     <row r="59" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>93</v>
@@ -6725,25 +6746,25 @@
         <v>139</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>1</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>108</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L59" s="4" t="s">
         <v>1</v>
@@ -6757,7 +6778,7 @@
     </row>
     <row r="60" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>93</v>
@@ -6769,7 +6790,7 @@
         <v>149</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>1</v>
@@ -6975,50 +6996,50 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7026,16 +7047,16 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7046,13 +7067,13 @@
         <v>86</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -7063,13 +7084,13 @@
         <v>86</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7302,282 +7323,282 @@
         <v>52</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25"/>
@@ -7798,277 +7819,277 @@
         <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="M4" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>1</v>
@@ -8077,162 +8098,162 @@
         <v>1</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>1</v>
@@ -8241,121 +8262,121 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>1</v>
@@ -8364,156 +8385,156 @@
         <v>1</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -8522,39 +8543,39 @@
         <v>1</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L18" s="4" t="s">
         <v>1</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
@@ -8566,36 +8587,36 @@
         <v>1</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>1</v>
@@ -8607,36 +8628,36 @@
         <v>1</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -8648,282 +8669,282 @@
         <v>1</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>579</v>
-      </c>
       <c r="M24" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>1</v>
@@ -8938,33 +8959,33 @@
         <v>1</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>1</v>
@@ -8979,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -9199,197 +9220,197 @@
         <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="7:7" x14ac:dyDescent="0.25"/>
@@ -9599,7 +9620,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9611,207 +9632,223 @@
         <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="25" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="26" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -2482,13 +2482,13 @@
     <t>consent</t>
   </si>
   <si>
-    <t>Ageing Navigator will use your answers to prepare a personalised Family Ageing Action Plan, which you receive as soon as you finish. Your answers are stored securely in Australia, seen only by the Ageing Navigator team, and deleted 12 months after your plan is sent, or sooner if you ask. We do not use AI, and we do not share your answers with anyone else without asking you first.</t>
+    <t>Your information is stored securely in Australia, kept for up to 12 months, and won’t be shared with other organisations without your permission.</t>
   </si>
   <si>
     <t>consent_checkbox</t>
   </si>
   <si>
-    <t>I agree, and I have the older person's agreement or am acting in their interests.</t>
+    <t>I agree, and I have the older person’s agreement or am acting in their interests.</t>
   </si>
   <si>
     <t>thank_you</t>
@@ -2570,7 +2570,7 @@
     <t>marketing_consent</t>
   </si>
   <si>
-    <t>Send me occasional news from Ageing Navigator. This is optional and you can stop at any time.</t>
+    <t>Send me occasional Ageing Navigator news. Optional.</t>
   </si>
   <si>
     <t>cta_stay_home</t>
@@ -2606,10 +2606,9 @@
     <t>questionnaire_intro</t>
   </si>
   <si>
-    <t xml:space="preserve">Tell us what's happening, and we'll help you work out what to do next.
-This questionnaire prepares your free personalised Family Ageing Action Plan. Depending on your situation it takes around 10 to 15 minutes, and you will only be shown questions that are relevant to you.
-You don't need to know every answer. “Not sure” is useful information too.
-Please don't include account numbers, passwords, detailed medical records or other highly confidential information.</t>
+    <t xml:space="preserve">Tell us what’s happening and we’ll help you work out what to do next with a free personalised Family Ageing Action Plan.
+It usually takes around 10 minutes, and you’ll only see questions relevant to your situation. It’s fine to choose “Not sure”.
+Please don’t include passwords, account numbers or detailed medical records.</t>
   </si>
   <si>
     <t>contact_intro</t>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="780">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -2627,6 +2627,12 @@
   </si>
   <si>
     <t>A needs assessment decides which level of care is needed, so the levels each home offers are shown.</t>
+  </si>
+  <si>
+    <t>contacts_intro</t>
+  </si>
+  <si>
+    <t>These organisations may be able to help with the actions in your plan. Services and contact details can change, so please check with each organisation directly.</t>
   </si>
   <si>
     <t>Label</t>
@@ -3457,7 +3463,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>96</v>
@@ -3465,10 +3471,10 @@
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>314</v>
@@ -3476,10 +3482,10 @@
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>81</v>
@@ -3487,10 +3493,10 @@
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>85</v>
@@ -3498,10 +3504,10 @@
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3533,13 +3539,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3547,16 +3553,16 @@
         <v>406</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3567,13 +3573,13 @@
         <v>636</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>729</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3581,16 +3587,16 @@
         <v>521</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3598,33 +3604,33 @@
         <v>613</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>609</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>609</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3632,16 +3638,16 @@
         <v>594</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3649,50 +3655,50 @@
         <v>532</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>744</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>741</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3700,16 +3706,16 @@
         <v>546</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3717,16 +3723,16 @@
         <v>462</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3734,16 +3740,16 @@
         <v>553</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3751,16 +3757,16 @@
         <v>580</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3768,16 +3774,16 @@
         <v>489</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3785,16 +3791,16 @@
         <v>512</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3802,50 +3808,50 @@
         <v>561</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3853,16 +3859,16 @@
         <v>452</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -9619,7 +9625,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9850,6 +9856,14 @@
         <v>711</v>
       </c>
     </row>
+    <row r="29" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
+++ b/deliverables/Ageing-Navigator-content-spreadsheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="782">
   <si>
     <t>Ageing Navigator content spreadsheet</t>
   </si>
@@ -2627,6 +2627,12 @@
   </si>
   <si>
     <t>A needs assessment decides which level of care is needed, so the levels each home offers are shown.</t>
+  </si>
+  <si>
+    <t>privacy_policy_url</t>
+  </si>
+  <si>
+    <t>/privacy</t>
   </si>
   <si>
     <t>contacts_intro</t>
@@ -3463,7 +3469,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>96</v>
@@ -3471,10 +3477,10 @@
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>314</v>
@@ -3482,10 +3488,10 @@
     </row>
     <row r="3" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>81</v>
@@ -3493,10 +3499,10 @@
     </row>
     <row r="4" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>85</v>
@@ -3504,10 +3510,10 @@
     </row>
     <row r="5" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -3539,13 +3545,13 @@
         <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3553,16 +3559,16 @@
         <v>406</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3573,13 +3579,13 @@
         <v>636</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3587,16 +3593,16 @@
         <v>521</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3604,33 +3610,33 @@
         <v>613</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>609</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>609</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3638,16 +3644,16 @@
         <v>594</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3655,50 +3661,50 @@
         <v>532</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>745</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>743</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3706,16 +3712,16 @@
         <v>546</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3723,16 +3729,16 @@
         <v>462</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3740,16 +3746,16 @@
         <v>553</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3757,16 +3763,16 @@
         <v>580</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3774,16 +3780,16 @@
         <v>489</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3791,16 +3797,16 @@
         <v>512</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3808,50 +3814,50 @@
         <v>561</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3859,16 +3865,16 @@
         <v>452</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -9625,7 +9631,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9864,6 +9870,14 @@
         <v>713</v>
       </c>
     </row>
+    <row r="30" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>715</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
